--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>45548</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44608</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45555</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45555</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45960</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>45713</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45587</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>45097</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45576</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45744</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>44572</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45320</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>46062</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>45720</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45141</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45845</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44154</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45539</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>46100</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>46043</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45320</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>46013</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>46106</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>45379</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44504</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>45446</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>44546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>45001</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>44573</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45744</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45936</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>45958</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>45541</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>45992</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45376</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>45133</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>46199</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>45567</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44893</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44609</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44837</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>44630</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44819</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44995</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44732</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44951</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45014</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45118</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45183</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45317</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45958</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>45232</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>45183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45559</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>45478</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>46062</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>46062</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45075</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>46182</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46196</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>46100</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>46100</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45034</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>44935</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>46244</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>46215</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>46215</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>44756</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45028</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>46266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>46276</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>46239</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>45799</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45370</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45880</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45883</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>46100</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44519</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>44550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>44791</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44621</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>44552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44582</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>44774</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44504</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>44552</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44860</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>44683</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>44833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44588</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>44552</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>44888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>44691</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>44552</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44750</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>44571</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44694</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>44866</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44528</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44839</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44664</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44571</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44517</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44502</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44750</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44722</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>44871</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>44519</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>44715</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>44515</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>44719</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44517</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>44517</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44615</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>44861</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>44525</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44728</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>44535</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44582</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44615</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>44749</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>44522</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44747</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44880</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>44732</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44839</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44879</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44722</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>44713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>44515</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>44713</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44819</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44879</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44505</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>44545</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44551</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44546</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44750</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44829</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44525</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44525</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44841</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44622</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44482</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44512</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>45229</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>45268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45415</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>44487</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>44599</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>45002</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44957</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45133</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>44831</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45641</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44531</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45769</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>44957</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>45604</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
         <v>45617</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17916,7 +17916,7 @@
         <v>45740</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45093</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>45306</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45405</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44741</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44768</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>44750</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45544</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44713</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44749</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45743</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44943</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45336</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44874</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45674</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45643</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45539</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45229</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45093</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45258</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45506</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45609</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45506</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45506</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45506</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45506</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>45293</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>44951</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45232</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20189,7 +20189,7 @@
         <v>45527</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>45467</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>44896</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45432</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>44823</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45610</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>44522</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44552</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>45751</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>44995</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>45086</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45629</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45461</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45103</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45002</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>44939</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45216</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>44768</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>44818</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44818</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44799</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45095</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44719</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45834</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45909</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45142</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44994</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>44552</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44874</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45356</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45593</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>44671</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45079</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45896</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45896</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22837,7 +22837,7 @@
         <v>45366</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
         <v>45169</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>44620</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45040</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45832</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45909</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45769</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45875</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45076</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45443</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45337</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45589</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45905</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45876</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45909</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45896</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45909</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45909</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>45909</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>45456</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24302,7 +24302,7 @@
         <v>45818</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45099</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>45916</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45916</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>44708</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>45372</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>45315</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45929</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45931</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44579</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45926</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45097</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>44489</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45371</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44995</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>44502</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45936</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44917</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45405</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45260</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45260</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>45939</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45425</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44592</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45943</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45943</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45314</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>46148</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45575</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45131</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44971</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>44704</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45406</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44518</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45471</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45960</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45722</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45960</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>44798</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45302</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>44880</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>45320</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45764</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45072</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45975</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45975</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45975</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45096</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45092</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45975</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45029</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45631</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>44852</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45980</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>45980</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>45980</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>45985</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45985</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45617</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45972</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>45281</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45281</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45985</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>45985</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44742</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45527</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>46160</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45593</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46142</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45278</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45866</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45574</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45127</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45993</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45993</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45643</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>44575</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45471</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45533</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45232</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45994</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46163</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45994</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>44861</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45195</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45994</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45315</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45740</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45616</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45698</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>46009</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45190</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>46009</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>44917</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>45183</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45183</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>44502</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44750</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>44907</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>46017</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>46017</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>46171</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45070</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45154</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>45229</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32397,7 +32397,7 @@
         <v>45229</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32470,7 +32470,7 @@
         <v>44699</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>45034</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46030</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>46030</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>46030</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>46171</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32908,7 +32908,7 @@
         <v>46034</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45152</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45096</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45702</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>46044</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>46048</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>46048</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>45737</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45315</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33570,7 +33570,7 @@
         <v>45470</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>46049</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>46052</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33789,7 +33789,7 @@
         <v>45630</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45044</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45574</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>44910</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>44893</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45098</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>46058</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>46058</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>46058</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>46058</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>46062</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>46061</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>46062</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>46062</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45027</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>46061</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>46061</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45539</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46061</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>46061</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>46061</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35332,7 +35332,7 @@
         <v>46061</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>46062</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>44530</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44691</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>46076</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46076</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>46183</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45541</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>46183</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45426</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45162</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45192</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45666</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>46086</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36354,7 +36354,7 @@
         <v>46090</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36427,7 +36427,7 @@
         <v>45625</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>44964</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>45467</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>46189</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>44888</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36792,7 +36792,7 @@
         <v>45785</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36865,7 +36865,7 @@
         <v>46092</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36938,7 +36938,7 @@
         <v>44540</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46098</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45007</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>46098</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>46097</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>46196</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>44575</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46100</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45619</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>44624</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44616</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>44719</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>46174</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>46111</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>46111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38116,7 +38116,7 @@
         <v>46111</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>46112</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>46111</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45609</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>46202</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>46244</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45350</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>46244</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>45097</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
         <v>46199</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45007</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38924,7 +38924,7 @@
         <v>44788</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>44855</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46126</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39148,7 +39148,7 @@
         <v>46202</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39226,7 +39226,7 @@
         <v>46199</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>44992</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44992</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         <v>46133</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
         <v>46132</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>44880</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>44749</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45618</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>45281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45698</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>44624</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45506</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45233</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>46204</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40258,7 +40258,7 @@
         <v>44917</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>44957</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         <v>45179</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40550,7 +40550,7 @@
         <v>46246</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>44893</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>46204</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45643</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>44704</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>44750</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>44904</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>45769</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>46248</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>45179</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45769</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>46206</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>45644</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>46205</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41572,7 +41572,7 @@
         <v>45647</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>46206</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41723,7 +41723,7 @@
         <v>46251</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45596</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45253</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>45405</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>44719</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45058</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>46253</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42234,7 +42234,7 @@
         <v>45728</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>45211</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45365</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>44917</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>46259</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>46259</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45333</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>44818</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>44973</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42896,7 +42896,7 @@
         <v>46259</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>44694</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45184</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43120,7 +43120,7 @@
         <v>44531</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>45463</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>44596</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>45720</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>44831</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44964</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>46221</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>46221</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>46222</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>46221</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>44893</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43923,7 +43923,7 @@
         <v>44893</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>46224</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>46224</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>46224</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45591</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>46224</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45735</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>46253</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45453</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>45546</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>46259</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45783</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45783</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44877,7 +44877,7 @@
         <v>46273</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44955,7 +44955,7 @@
         <v>46273</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45033,7 +45033,7 @@
         <v>46273</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>45541</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45281</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46279</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>46276</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>46276</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>44970</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45569</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45505</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46276</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45783,7 +45783,7 @@
         <v>45786</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45786</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>46279</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>46279</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46075,7 +46075,7 @@
         <v>46280</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>45786</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>46281</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>45734</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46377,7 +46377,7 @@
         <v>46280</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>46281</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>46281</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45793</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>45769</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>45793</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>45726</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45085</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>46280</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45618</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47117,7 +47117,7 @@
         <v>45799</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45818</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45643</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45825</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45835</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>45845</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>45866</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45834</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45680</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45834</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>44972</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45876</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45880</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48091,7 +48091,7 @@
         <v>45568</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>44601</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45195</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45195</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45678</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>46089</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>46100</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>45548</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44608</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45555</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45960</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45587</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>45555</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>45576</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45320</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>46062</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45845</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45744</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45720</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45141</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44154</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45539</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>46100</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45320</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45379</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>46106</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>45446</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>44504</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45324</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44893</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45799</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>45936</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45958</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45001</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45133</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>46199</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44965</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44609</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45883</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45183</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44935</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>46062</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45370</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>46062</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45183</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>46100</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>46100</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44951</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45075</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45014</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45559</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>46182</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45034</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>46196</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>45880</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45478</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>46215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>46215</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>46266</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44756</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45317</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>46239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>46244</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44995</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44732</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45118</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>46100</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44519</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44552</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44582</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44621</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44558</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44504</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44774</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44552</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44860</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44552</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44552</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44888</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44691</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>44552</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>44750</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44571</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44694</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44866</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44528</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44839</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44664</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>44517</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44502</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44750</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44722</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44871</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44519</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44715</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44719</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44517</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44615</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44861</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44525</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44535</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44582</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44522</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44747</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44880</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44879</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44515</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44819</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44879</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>44545</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>44505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44829</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>44525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44622</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>44512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>44742</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45471</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45337</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45467</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45619</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>44823</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45432</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45461</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45278</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45302</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45539</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>44768</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45372</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44893</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44893</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45260</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45260</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44552</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45793</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46017</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>46017</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45533</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45085</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45793</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45726</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>46030</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45769</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44540</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45356</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45618</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45162</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46030</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44893</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>46034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45834</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>44874</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45896</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45896</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>44893</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44855</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45799</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46044</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>46048</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44671</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>44599</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46049</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45443</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45366</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>46052</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45909</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45643</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45643</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45909</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45876</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45405</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45909</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45909</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>46058</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44917</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45618</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45007</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46062</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>46061</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45604</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>46062</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>46062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>46061</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>46061</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>46061</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45666</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>46061</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>46061</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>46061</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>44552</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44910</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44937</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45350</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45333</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45092</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45232</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>46076</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45926</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45929</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45152</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45195</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45169</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45931</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45527</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>46086</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44596</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>46090</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44694</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>46092</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46097</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>46098</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45698</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46098</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45943</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45943</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45229</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45609</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46111</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>46111</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45751</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46111</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>46111</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45506</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>46112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45960</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>44798</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44704</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>46126</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45127</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45975</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45975</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45975</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45975</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45610</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>45371</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44917</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>44964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46132</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45980</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44880</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45980</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46133</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45985</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45972</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45985</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45985</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45609</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45674</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44768</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45698</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45993</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45994</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44818</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45994</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45993</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44719</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>44896</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>44818</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45818</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>44852</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45832</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>46009</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44522</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45769</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45875</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45909</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45909</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45467</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44861</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45643</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45825</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45743</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45007</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45044</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45232</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45737</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45818</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45769</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45070</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46148</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45079</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45096</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>44880</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45086</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45258</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45740</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>44531</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45835</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>46142</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45099</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>46160</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45866</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45596</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45617</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45002</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45527</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45845</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44518</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45336</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46163</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45093</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44502</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44973</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>44831</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46171</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45769</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45593</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46171</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45866</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45575</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45405</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>44951</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45574</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45281</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45834</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>45834</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44530</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44972</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45680</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46183</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46183</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45617</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45426</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>45179</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45179</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45405</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>46189</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45131</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45722</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44487</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45539</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45616</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45876</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45643</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46174</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45631</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45880</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45506</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45415</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>46199</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46199</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44579</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45625</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45506</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45506</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45506</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45506</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45568</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46202</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44624</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45281</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45281</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>46204</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46204</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46205</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45098</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45095</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46206</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44704</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46251</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>46253</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45629</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>44708</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45133</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45190</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45192</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44713</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45097</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46259</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>46259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>45183</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45183</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>44749</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46259</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45253</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>44749</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45463</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>46221</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44750</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45306</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45735</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46224</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>46221</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46221</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46222</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>46224</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46224</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45702</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45315</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46224</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>45740</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>45320</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44917</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45233</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46253</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45229</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45229</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>44750</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>44904</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>44818</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>46273</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>46273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46273</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46259</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>44994</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>44917</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>46276</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>44939</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>46276</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45728</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45644</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>46276</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45293</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46280</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>45076</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46280</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46279</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46279</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>46279</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44502</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>44620</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45406</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45216</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>44799</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>46281</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45630</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45211</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45471</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>44719</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44907</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>44552</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44957</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>44575</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>46244</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>46281</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>44831</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>44992</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44992</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>46246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>46280</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>46244</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>46289</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>46289</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45593</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46248</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45591</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45183</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45425</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44750</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>44616</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45546</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>44691</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45072</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45072</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>44624</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>44531</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45589</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44995</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44995</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44964</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45040</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45736</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45470</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45541</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44575</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45058</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>44957</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>44957</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45154</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>44489</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45720</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44719</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45027</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45034</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45641</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44788</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>44971</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44741</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45142</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45002</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45544</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45365</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45103</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45029</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44592</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45647</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44699</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45097</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45314</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45643</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45456</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45268</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45229</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45769</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45315</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45574</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45184</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45453</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45783</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45783</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45541</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45786</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45281</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45786</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45786</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44970</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45505</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45569</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45734</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44601</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45195</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45678</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46089</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46100</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>45548</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>44608</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45555</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45960</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45587</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>45555</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>45576</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44552</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>45320</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>46062</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45845</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45744</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45720</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>45141</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44154</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>45539</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>46100</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45320</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45379</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>46106</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>45446</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>44504</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45324</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45107</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45376</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>44893</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>45884</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45799</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>45936</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45958</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45001</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45133</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44573</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>46199</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>45744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44965</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44609</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45883</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45183</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44935</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>46062</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45370</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>46062</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45183</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45944</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>46100</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>46100</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45958</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44951</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45075</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45014</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45559</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>46182</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45034</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>46196</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>45880</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45478</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>46215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>46215</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>46266</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44756</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45317</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>46239</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>46244</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>44995</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44732</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45118</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>46100</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44519</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11283,7 +11283,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44552</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>44582</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44621</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44558</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44504</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44774</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>44552</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44860</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44552</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44552</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>44888</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>44691</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>44552</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>44750</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44571</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44694</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44866</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44528</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44839</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44664</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>44517</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44502</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44750</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44722</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44871</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44519</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44715</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44719</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44517</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>44615</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44861</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44525</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>44728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>44535</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44582</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>44615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44522</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44747</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44880</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
         <v>44879</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>44722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44515</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>44819</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44879</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>44545</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>44505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>44750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44829</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>44525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44622</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>44512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>44742</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45471</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45337</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>45467</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45619</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>44823</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45432</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45461</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45278</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45302</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45539</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>44768</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45372</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44893</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>44893</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44943</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45260</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45260</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>44552</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45793</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46017</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>46017</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45533</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45085</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45793</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45726</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>46030</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45769</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44540</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45356</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45618</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45162</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46030</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44893</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>46034</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>44888</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45834</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>44874</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45896</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45896</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>44893</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44855</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44874</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>45799</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>46044</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
         <v>46048</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44671</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>44599</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46049</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45443</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45366</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>46052</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45905</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45909</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45643</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>45643</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45909</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45876</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45405</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45909</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45909</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>46058</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>46058</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>44917</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45618</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45007</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46062</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>46061</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45604</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>46062</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>46062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>46062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>46061</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>46061</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>46061</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45666</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22560,7 +22560,7 @@
         <v>46061</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>46061</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>46061</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>44552</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>44910</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44937</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45350</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45333</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>45092</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45232</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>46076</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>45926</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45929</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>45152</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>45195</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>45169</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>45931</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45527</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>46086</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>44596</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>46090</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>44694</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>46092</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>46097</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>46098</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45698</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>46098</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45943</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45943</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>45229</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>46100</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45609</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46111</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>46111</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45751</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46111</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>46111</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45506</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>46112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45960</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45960</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>44798</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>44704</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45764</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>46126</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45127</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45975</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>45975</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45975</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45975</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45610</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>45371</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44917</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>44964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>46132</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45980</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44880</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45980</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46133</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>45985</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45972</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45985</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45985</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45609</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45674</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44768</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45698</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45993</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45994</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>45994</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44818</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45994</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>45993</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44719</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>44896</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>44818</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45818</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>44852</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45832</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>46009</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44522</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>46009</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>45769</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>45875</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45909</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45909</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>45467</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44861</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45643</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>45825</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45743</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45007</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45044</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45232</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45737</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45818</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45769</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45070</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46148</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45079</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>45096</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>44880</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45086</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45258</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45740</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>44531</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45835</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>46142</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45099</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>46160</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45866</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45596</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45617</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>45002</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45527</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45845</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>44518</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>45336</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46163</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45093</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44502</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44973</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>44831</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46171</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45769</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45593</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46171</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45866</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45575</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45405</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>44951</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45574</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45281</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45834</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>45834</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>44530</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>44972</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45680</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>46183</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>46183</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45617</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33474,7 +33474,7 @@
         <v>45426</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>45179</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45179</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45405</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45167</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>46189</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45131</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45722</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44487</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>45539</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>45616</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45876</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45643</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46174</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45631</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>45880</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45506</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45415</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>46199</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46199</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>44579</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45625</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45506</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45506</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45506</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45506</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45568</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46202</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>44624</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45281</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45281</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>46204</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>46204</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>46205</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45098</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45095</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
         <v>46206</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46206</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>44704</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46251</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>46253</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45629</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>44708</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45133</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45190</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45192</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44713</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45097</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46259</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37363,7 +37363,7 @@
         <v>46259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37436,7 +37436,7 @@
         <v>45183</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45183</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>44749</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46259</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45253</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>44749</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45463</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>46221</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44750</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45306</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45735</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46224</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>46221</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>46221</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38468,7 +38468,7 @@
         <v>46222</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>46224</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>46224</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45702</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45315</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>46224</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>45740</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>45320</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44917</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39130,7 +39130,7 @@
         <v>45233</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>46253</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45229</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45229</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>44750</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>44904</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>44818</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>46273</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>46273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46273</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39875,7 +39875,7 @@
         <v>46259</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>44994</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
         <v>44917</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>46276</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>44939</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>46276</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45728</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45644</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>46276</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45293</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46280</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>45076</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46280</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46279</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40927,7 +40927,7 @@
         <v>46279</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41000,7 +41000,7 @@
         <v>46279</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41073,7 +41073,7 @@
         <v>44502</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>44620</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45406</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45216</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>44799</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>46281</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>45630</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45211</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45471</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41813,7 +41813,7 @@
         <v>44719</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>44907</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41959,7 +41959,7 @@
         <v>44552</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44957</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>44575</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42178,7 +42178,7 @@
         <v>46287</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>46244</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>46281</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>44831</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>44992</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>44992</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>46246</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42689,7 +42689,7 @@
         <v>46280</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>46244</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>46289</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>46289</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45593</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46248</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>45591</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45183</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45425</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44750</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>44616</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45546</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>44691</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45072</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45072</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>44624</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>44531</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45589</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44995</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44995</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44964</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45040</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45736</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45470</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45541</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44575</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45058</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>44957</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>44957</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45154</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>44489</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45720</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>44719</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45027</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45034</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45641</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>44788</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>44971</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44741</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45142</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45002</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45544</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>45365</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45103</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45029</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44592</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45647</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>44699</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45097</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45314</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45643</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>45456</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45268</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>45229</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45769</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45315</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45574</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45184</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>45453</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47270,7 +47270,7 @@
         <v>45783</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45783</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47416,7 +47416,7 @@
         <v>45541</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47489,7 +47489,7 @@
         <v>45786</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>45281</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>45786</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>45786</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>44970</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45505</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45569</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>45734</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44601</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45195</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45678</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46089</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>46100</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45555</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45555</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45587</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45713</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46062</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45744</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>44572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45320</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45720</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45141</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45539</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>46146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45446</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45320</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45379</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44504</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45884</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45799</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45001</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45936</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45958</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45992</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44573</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45744</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45042</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>44965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45541</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>45376</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>46199</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45567</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44893</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45370</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>46062</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>46062</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44951</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45014</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>46100</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45118</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>45183</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45317</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45232</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45559</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45183</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45880</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45883</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>46196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>45478</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>46215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>46215</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45075</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>46266</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>46239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>46244</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>46293</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44756</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45028</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46100</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44550</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44519</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44552</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44621</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44582</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>44504</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44552</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44860</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44588</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44552</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>44774</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44552</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44750</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>44571</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44694</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44866</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44528</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44839</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44664</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44517</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>44502</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>44750</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44871</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44519</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>44722</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44715</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44719</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44517</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>44615</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44861</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44525</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44535</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44582</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44522</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44747</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>44552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44880</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44879</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44515</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44819</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44879</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44545</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>44505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>44750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44829</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>44841</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>44525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>44622</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>44525</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>44512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45229</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44487</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45415</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45093</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45002</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44599</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44957</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44831</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45133</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45604</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45769</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44937</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45641</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44957</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45786</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45786</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45405</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45544</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45306</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45786</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45734</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44768</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45539</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>46009</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>44741</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46009</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>44750</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45834</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>44713</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>44749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>46017</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>46017</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45743</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44874</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45183</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44943</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45336</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44874</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45896</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45896</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>46030</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>46030</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>46030</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45674</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46034</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45643</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45793</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45443</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45093</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45769</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45905</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45793</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45876</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45229</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45909</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45909</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45258</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45909</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45909</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45085</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>46044</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46048</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45506</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45506</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45506</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45506</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45506</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45916</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45618</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45799</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45609</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45293</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>46052</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45232</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45929</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45931</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44951</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>46058</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>46062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45926</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>46061</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>46062</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>46061</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>46061</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>46061</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>46061</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46061</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>46061</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>46062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45527</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45467</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44896</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45939</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45943</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45943</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45432</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>46076</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44823</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45282</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>46086</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45610</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45751</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>45960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45960</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>44522</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44552</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46092</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>44995</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46098</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45764</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>46098</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45086</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45629</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45002</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>46100</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45975</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45975</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45975</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45818</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45461</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45980</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45980</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45985</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46111</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>46111</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45972</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45985</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45985</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46111</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46112</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46111</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45643</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45103</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44939</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45993</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45993</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45216</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>44768</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45994</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44799</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45095</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>46126</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45994</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44719</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>46133</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>46132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45698</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45142</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44994</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45356</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45593</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>44671</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45835</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45079</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45366</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45169</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44620</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45040</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45337</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45589</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>44818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44818</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45909</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45456</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45099</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44708</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45372</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45315</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45832</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45909</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45769</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45875</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44579</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45736</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45097</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44489</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45371</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44995</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>44502</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45818</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>44917</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45405</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45260</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45260</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45425</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44592</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>45866</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>45834</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45314</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45575</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45680</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45834</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45131</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>44971</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44704</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44972</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>46148</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45406</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44518</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>45471</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45722</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>44798</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45302</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44880</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45320</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45866</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45072</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45072</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45876</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45096</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>45092</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46163</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45631</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44852</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>45880</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45617</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45281</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>44742</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45527</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46171</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45593</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45278</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45574</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45127</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45568</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45643</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45643</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44552</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44575</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>45471</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45533</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>45232</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>44861</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45195</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46183</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>46183</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45315</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>44552</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>46189</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45740</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>45785</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45616</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45698</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>46196</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45190</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44917</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45183</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45183</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44502</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44750</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>44907</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46174</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>46199</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>45154</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45229</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45229</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>44699</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>46202</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>46199</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45034</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>46204</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>46204</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>44704</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>46206</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46205</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45152</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>46206</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45096</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>46259</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46259</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45702</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46259</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45737</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45315</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45470</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45630</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>45044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>46221</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46221</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>46222</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>46221</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45574</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>44910</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>44893</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45098</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45027</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45539</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46224</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>46224</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46224</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46224</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44530</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>44691</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46259</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>46273</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45541</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>46273</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>46273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45426</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45162</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45192</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>46279</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>46276</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>46276</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>46276</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45666</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46279</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46279</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>46280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>46281</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>46280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45625</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44964</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45467</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>44888</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>44540</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>45007</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45007</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>44575</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45619</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46287</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>44624</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>44616</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46244</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46244</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>44719</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46281</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>46246</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>46280</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>45609</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45350</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45097</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45007</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>44788</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45546</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44855</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>44992</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>44992</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46293</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44749</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45618</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>46248</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45281</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>46062</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>44624</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45506</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45233</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46295</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>46295</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>46295</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>44917</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>44957</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45167</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>45179</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>46295</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46289</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>46289</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>44893</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>46253</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45643</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>44750</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44904</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45769</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45179</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46253</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45769</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46289</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>46289</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45644</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45647</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45596</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45253</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45405</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>44719</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45058</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45728</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45211</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45365</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>44917</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45333</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>44818</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>44973</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44694</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45184</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>44531</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45463</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>44596</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45720</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>44831</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>44964</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>44893</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>44893</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45591</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45735</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45453</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45783</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45783</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45541</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45281</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>44970</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45569</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45505</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>44601</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45195</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45195</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45678</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>46089</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>46100</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45555</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45555</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45587</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>45713</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46062</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45744</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>45845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>44572</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45320</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45720</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45141</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45539</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>46146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46106</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45446</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>46043</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45320</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45379</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>44504</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45884</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45799</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45001</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45936</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45958</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45992</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>44573</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45744</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45042</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>44965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45541</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>45376</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>46199</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45567</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44893</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45799</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45370</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>44732</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>46062</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>46062</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>44951</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45014</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>46100</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45118</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>45183</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45317</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45232</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45559</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45183</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45880</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45883</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>46196</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>45478</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>46215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>46215</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45075</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>46266</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>46239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>46244</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>46293</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44756</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45028</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46100</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44550</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44519</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44552</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44791</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44621</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>44582</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>44504</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44552</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44860</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44588</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44552</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>44774</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44552</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44750</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>44571</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44694</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44588</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44866</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44528</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44839</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44664</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44517</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>44502</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>44750</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>44871</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44519</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>44722</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44715</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44515</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44719</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44517</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>44615</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44861</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44525</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44535</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44582</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>44749</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>44522</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44747</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>44552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44880</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44517</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44879</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44515</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44713</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44819</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44879</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>44545</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>44505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44551</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>44750</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44829</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>44841</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>44525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>44622</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>44525</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44482</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>44512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45229</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>44487</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45415</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45093</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45002</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44599</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44957</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>44831</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45133</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45604</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45769</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17655,7 +17655,7 @@
         <v>45617</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>44937</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45641</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44957</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45786</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>45786</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18093,7 +18093,7 @@
         <v>45405</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45544</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>45306</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45786</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45734</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44768</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45539</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>46009</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>44741</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46009</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>44750</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45834</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>44713</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>44749</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>46017</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>46017</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45743</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>44874</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45183</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44943</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45336</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>44874</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45896</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>45896</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>46030</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>46030</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>46030</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45674</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>46034</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>45643</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45793</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45443</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45093</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>45769</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45905</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45793</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45876</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45229</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45909</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45896</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>45909</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45258</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>45909</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>45909</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45085</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>46044</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46048</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45506</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>45506</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45506</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>45506</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45506</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45916</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45916</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>45618</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45799</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22264,7 +22264,7 @@
         <v>45609</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22337,7 +22337,7 @@
         <v>45293</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22410,7 +22410,7 @@
         <v>46052</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45232</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45929</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>45931</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>44951</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>46058</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>46062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45926</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22994,7 +22994,7 @@
         <v>46061</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>46062</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>46061</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>46061</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
         <v>46061</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>46061</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46061</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>46061</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>46062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45936</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45527</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>45467</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>44896</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45939</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45943</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45943</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45432</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>46076</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44823</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45282</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>46086</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45610</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45751</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45960</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>45960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45960</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>44522</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44552</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46092</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>44995</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46098</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>45764</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>46098</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45086</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45629</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45002</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>46100</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45975</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45975</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45975</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45818</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45461</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45980</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45980</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45985</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>46111</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>46111</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45972</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45985</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45985</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>46111</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46112</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46111</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45643</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45103</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44939</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45993</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45993</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45216</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>44768</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45994</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45994</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44799</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45095</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>46126</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45994</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44719</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>46133</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>46132</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45698</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45142</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44994</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45356</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45593</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>44671</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>45835</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45079</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45366</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45169</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44620</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>45040</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45337</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45589</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>44818</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>44818</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45845</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45909</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45456</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45099</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44708</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45372</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45315</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45832</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45909</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45769</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45875</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44579</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45736</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45097</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44489</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45371</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44995</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>44502</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>45818</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>44917</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45405</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45260</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45260</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45425</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44592</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>45866</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>45834</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45314</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45575</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45680</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45834</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45131</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>44971</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>44704</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>44972</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>46148</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45406</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44518</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>45471</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45722</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>44798</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45302</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44880</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32803,7 +32803,7 @@
         <v>45320</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46142</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45866</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45072</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45072</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45876</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33324,7 +33324,7 @@
         <v>45096</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>45092</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45029</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>46163</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45631</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44852</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>45880</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>45617</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45281</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>45281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>44742</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45527</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>46171</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>46171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34361,7 +34361,7 @@
         <v>45593</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45278</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34507,7 +34507,7 @@
         <v>45574</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45127</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45568</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45643</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45643</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34872,7 +34872,7 @@
         <v>44552</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44575</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35018,7 +35018,7 @@
         <v>45471</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35091,7 +35091,7 @@
         <v>45533</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>45232</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>44861</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45195</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46183</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>46183</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45315</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>44552</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>46189</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45740</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35821,7 +35821,7 @@
         <v>45785</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45616</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35967,7 +35967,7 @@
         <v>45698</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>46196</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36118,7 +36118,7 @@
         <v>45190</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44917</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>45183</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
         <v>45183</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>44502</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44750</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>44907</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>46174</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>46202</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>46199</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>45154</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45229</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45229</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>44699</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>46202</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>46199</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45034</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>46204</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>46204</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>44704</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>46206</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>46205</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45152</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>46206</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45096</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>46259</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46259</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45702</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46259</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45737</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45315</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>45470</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45630</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>45044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>46221</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>46221</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>46222</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>46221</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45574</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>44910</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>44893</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45098</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45027</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>45539</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>46224</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>46224</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>46224</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46224</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>44530</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>44691</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>46259</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>46273</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45541</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>46273</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>46273</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45426</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45162</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45192</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>46279</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>46276</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>46276</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>46276</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>45666</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>46279</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>46279</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>46280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>46281</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>46280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45625</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44964</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41371,7 +41371,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41444,7 +41444,7 @@
         <v>45467</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41517,7 +41517,7 @@
         <v>44888</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>44540</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>45007</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>45007</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>44575</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45619</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46287</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>44624</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>44616</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>46244</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>46244</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>44719</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>46281</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42466,7 +42466,7 @@
         <v>46246</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42539,7 +42539,7 @@
         <v>46280</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>45609</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45350</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45097</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45007</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>44788</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45546</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>44855</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>44992</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>44992</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46293</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44749</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45618</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>46248</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45281</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>46062</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>44624</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45506</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>45233</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>46251</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46295</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>46295</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44243,7 +44243,7 @@
         <v>46295</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>44917</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>44957</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45167</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44540,7 +44540,7 @@
         <v>45179</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44613,7 +44613,7 @@
         <v>46295</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44691,7 +44691,7 @@
         <v>46289</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>46289</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44847,7 +44847,7 @@
         <v>44893</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>46253</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45643</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45066,7 +45066,7 @@
         <v>44750</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44904</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45769</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45179</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>46253</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45769</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>46289</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
         <v>46289</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45644</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45733,7 +45733,7 @@
         <v>45647</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45596</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45253</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45405</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46030,7 +46030,7 @@
         <v>44719</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46103,7 +46103,7 @@
         <v>45058</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45728</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45211</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45365</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46400,7 +46400,7 @@
         <v>44917</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>45333</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>44818</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>44973</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>44694</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45184</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>44531</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45463</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>44596</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45720</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         <v>44831</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47208,7 +47208,7 @@
         <v>44964</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47281,7 +47281,7 @@
         <v>44893</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>44893</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45591</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45735</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>45453</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>45783</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45783</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>45541</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45281</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>44970</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48016,7 +48016,7 @@
         <v>45569</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>45505</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>44601</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>45195</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45195</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45678</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48454,7 +48454,7 @@
         <v>46089</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>46100</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44608</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>45555</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45555</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45320</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>44572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45744</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45720</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>46062</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45539</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>46146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45320</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>44504</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45379</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>45446</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>46106</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45107</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44893</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45042</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45376</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45884</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45936</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>45799</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45567</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45958</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45001</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45744</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45992</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44965</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>46199</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44630</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44609</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44732</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45883</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45118</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45232</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45183</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>45370</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45944</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45944</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45958</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>45028</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44756</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45880</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45075</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45317</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45014</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44995</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45559</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>46182</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>46196</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>46266</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>46239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>46244</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>46293</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>46062</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>46303</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>46215</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>46100</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>44550</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>44519</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44791</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44621</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44552</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44558</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44504</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44774</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44552</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44860</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44588</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44552</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44888</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44552</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>44750</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44571</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44694</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44866</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44528</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44839</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44664</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44517</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44861</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44879</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44880</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44545</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44505</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44750</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44551</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44546</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44839</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44732</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44722</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44728</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44879</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44871</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44519</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44722</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44535</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44715</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44515</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44719</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44517</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44615</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44517</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44829</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44525</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44525</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44749</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44515</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44841</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44615</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44522</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44747</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45079</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44482</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44719</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44823</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45096</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44512</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45027</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44880</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45432</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45086</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45471</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45034</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45619</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45641</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45258</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44788</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45337</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44971</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45740</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44741</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45099</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45596</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>45461</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45302</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45278</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45539</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45467</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45002</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45617</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45372</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45544</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44893</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>44768</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45002</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45527</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44518</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45336</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45093</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44502</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45365</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>44943</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>44973</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45103</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45260</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45260</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45029</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44552</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44592</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45647</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45533</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44699</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44831</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45769</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45593</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45314</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45834</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45643</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45456</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>44540</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45356</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45268</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44874</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45575</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45229</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45405</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45162</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>44951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45896</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45769</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44893</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44888</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45574</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45281</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45443</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44893</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>44855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>44874</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45315</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45905</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>44530</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45574</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45909</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45876</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45896</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45909</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45453</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44671</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45282</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44599</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45366</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45783</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45783</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45643</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45643</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45916</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45916</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45617</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45541</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45405</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45786</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45281</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45426</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44917</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45786</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45786</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45618</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45179</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45179</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45007</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45007</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45405</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45604</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45167</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45666</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>44552</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>44910</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45131</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44970</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44937</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45350</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45722</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44487</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45333</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45315</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45505</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45569</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45539</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45734</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45092</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45616</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45643</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45232</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45926</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45793</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45929</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45085</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45631</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45152</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45506</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45415</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45793</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45726</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45769</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45169</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44579</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45527</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45625</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45506</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45506</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45506</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45506</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45931</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45618</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>44596</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>44624</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45936</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44694</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>45281</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45281</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45799</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45698</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45229</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45098</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45095</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45609</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45939</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45943</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45943</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45751</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45629</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45506</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44708</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45133</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45190</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45192</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44798</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44713</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45097</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45643</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45825</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44704</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45183</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45183</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>44749</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45960</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45960</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45127</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44749</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45835</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45610</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45463</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45371</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44917</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>44964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>44880</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45096</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>44750</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45845</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45764</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45609</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45674</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45306</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>45735</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44768</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45702</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45315</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>44719</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45740</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44896</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45320</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>44917</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44852</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45866</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45975</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45233</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45975</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45834</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45834</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44972</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45680</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45229</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44750</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>44904</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45980</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44818</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>44522</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45876</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45980</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45980</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>44994</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45880</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>44917</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45568</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44939</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45467</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45728</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45644</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>46097</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44861</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45293</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>46098</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>46098</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45076</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45743</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44502</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45007</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45972</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45985</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44620</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45985</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>45985</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45406</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>45216</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45044</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45232</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>44799</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45737</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>46111</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>46111</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>46111</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45769</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45630</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>46111</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>45211</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>45070</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>46112</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45471</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45993</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44719</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>44907</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45994</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45994</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>45994</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>45993</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44552</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>44957</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>44575</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>46132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>44831</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>44992</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44992</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>46133</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45593</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>45591</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45183</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>46009</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45698</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46009</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>44818</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>45425</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>46017</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>46017</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44750</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>44616</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>44818</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>44691</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45072</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45072</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>46030</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45832</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>46030</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>44624</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>44531</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45589</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>44995</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>44995</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>46034</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>44964</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45040</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45736</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45470</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45541</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44575</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45058</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>44957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>44957</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45154</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45769</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>44489</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>45875</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45909</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45909</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>46044</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>46048</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45720</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46052</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>46058</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45818</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>46062</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46061</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>46061</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>46061</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>46061</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>46061</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>46061</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>46061</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>46148</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>46086</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>46142</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>46160</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45866</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>46092</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>46163</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>46171</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>46171</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>46183</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>46183</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45785</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>46189</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>46196</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>46174</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>46199</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>46199</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>46202</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>46202</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>46204</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46204</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>46205</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>46206</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>46206</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44704</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>46221</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>46224</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>46221</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>46221</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46222</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>46224</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46224</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46224</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>46273</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>46273</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>46273</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>46276</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46276</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>46276</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>46280</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>46280</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45296,7 +45296,7 @@
         <v>46279</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>46279</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>46279</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>46281</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>46281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>46287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>46244</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>46246</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>46280</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>46244</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>46062</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>46248</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>46293</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>46253</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>46251</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>46295</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>46295</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>46295</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>46295</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>46289</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>46253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>46289</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46289</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46289</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>46259</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>46302</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>46302</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>46259</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>46259</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>46302</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>46302</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>46302</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>46259</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45546</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>44601</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45195</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45678</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46089</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>46100</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44608</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45713</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>45555</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45555</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45320</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>44572</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>45845</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>45744</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45720</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>46062</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45539</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>46146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45320</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>44504</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45379</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>45446</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>46106</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>45107</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44893</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>45042</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>45376</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45884</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45936</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>45799</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45567</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45958</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45001</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45744</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>45133</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>45992</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>45541</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44965</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>46199</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44630</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44819</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>44609</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44732</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45883</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45118</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45232</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45183</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45478</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45799</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>45370</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45944</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>45944</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45958</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44951</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>45028</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44756</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45880</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45075</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>46100</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45317</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45014</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44995</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45559</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>46182</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>46196</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>46266</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>46239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>46244</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>46293</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>46062</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>46303</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>46215</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>46100</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>44550</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>44519</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44791</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44621</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44552</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44558</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44504</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44774</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44552</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44860</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44683</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44833</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44588</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44552</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44888</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>44691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44552</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>44750</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44571</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44602</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>44694</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44866</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44528</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44839</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44664</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44517</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44839</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44861</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44879</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44880</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44545</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44505</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44750</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44551</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44525</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44546</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44839</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44732</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44722</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44728</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>44879</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>44871</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44519</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44722</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44535</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44582</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44715</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44515</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44719</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44517</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44615</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>44517</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44829</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44525</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>44525</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44749</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44515</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>44841</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44615</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44522</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>44622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>44747</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45079</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44482</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44719</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44823</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>45096</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44512</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45027</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44880</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45432</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45086</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>45471</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45034</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45619</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45641</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45258</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44788</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45337</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44971</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45740</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44741</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45099</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45596</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>45461</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45302</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45278</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45539</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45467</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>45002</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45617</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45372</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45544</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44893</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44893</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>44768</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45002</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45527</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>44518</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45336</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45093</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44502</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45365</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>44943</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>44973</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45103</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45260</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45260</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45029</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44552</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>44592</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45647</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45533</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44699</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44831</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45769</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>45593</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45314</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>45834</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45643</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45456</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>44540</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         <v>45356</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45268</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44874</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>45575</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45229</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45405</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45162</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>44951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45896</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45896</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45769</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>44893</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>44888</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>45574</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45281</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45443</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>44893</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>44855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>44874</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45315</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22554,7 +22554,7 @@
         <v>45905</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22627,7 +22627,7 @@
         <v>44530</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22700,7 +22700,7 @@
         <v>45909</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>45574</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45909</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45876</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45896</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45909</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45453</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>44671</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45282</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>44599</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45366</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45783</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45783</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45643</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45643</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45916</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45916</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45617</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45541</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45405</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45786</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45281</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45426</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>44917</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45786</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45786</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45618</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45179</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45179</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45007</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45007</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45405</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45604</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45167</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45666</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>44552</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>44910</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45131</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44970</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44937</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45350</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45722</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44487</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45333</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45315</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45505</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45569</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45539</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45734</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45092</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>45616</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45643</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45232</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45926</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45793</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45929</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45085</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45631</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45152</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45195</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45506</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45415</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45793</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45726</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>45769</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45169</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44579</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45527</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45625</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45506</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45506</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45506</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45506</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45931</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45618</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>44596</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>44624</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45936</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>44694</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>45281</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45281</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45799</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45698</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45229</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>45098</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45095</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45609</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45939</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45943</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45943</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45751</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45629</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45506</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44708</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45818</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45133</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45190</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45192</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44798</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44713</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45097</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45643</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45825</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44704</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45183</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45183</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>44749</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45960</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45960</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45960</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45127</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44749</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45835</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45610</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45463</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45371</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>44917</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>44964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>44880</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45096</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>44750</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45845</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45764</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45609</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>45674</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45306</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>45735</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44768</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45702</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45315</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32474,7 +32474,7 @@
         <v>44719</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45740</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>44896</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45320</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32771,7 +32771,7 @@
         <v>44917</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         <v>44852</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         <v>45866</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>45975</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45233</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45975</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45834</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45834</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44972</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>45680</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45229</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44750</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>44904</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>45980</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44818</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>44522</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45876</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45980</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45980</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>44994</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45880</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>44917</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45568</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44939</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45467</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45728</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45644</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>46097</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44861</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45293</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>46098</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>46098</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45076</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45743</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45985</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44502</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45007</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45972</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45985</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44620</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45985</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>45985</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45406</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>45216</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45044</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45232</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>44799</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45737</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>46111</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>46111</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>46111</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45769</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45630</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>46111</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>45211</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>45070</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>46112</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45471</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45993</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44719</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>44907</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45994</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37342,7 +37342,7 @@
         <v>45994</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>45994</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>45993</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>44552</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>44957</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>44575</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>46126</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>46132</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>44831</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>44992</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44992</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>46133</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45593</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>45591</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45183</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>46009</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45698</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46009</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>44818</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>45425</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>46017</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>46017</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>44750</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>44616</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>44818</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>44691</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45072</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45072</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>46030</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>46030</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>45832</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>46030</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39683,7 +39683,7 @@
         <v>44624</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>44531</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39829,7 +39829,7 @@
         <v>45589</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>44995</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>44995</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>46034</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>44964</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45040</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45736</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45470</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45541</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40486,7 +40486,7 @@
         <v>44575</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45058</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         <v>44957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>44957</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45154</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45769</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>44489</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>45875</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>45909</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41148,7 +41148,7 @@
         <v>45909</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>46044</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>46048</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>45720</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46052</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>46058</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45818</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>46062</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>46061</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>46061</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41878,7 +41878,7 @@
         <v>46061</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>46061</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42024,7 +42024,7 @@
         <v>46061</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         <v>46061</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>46061</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>46148</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>46086</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>46142</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>46160</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45866</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>46092</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>46163</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>46171</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>46171</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>46183</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>46183</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45785</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>46189</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>46196</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>46174</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43348,7 +43348,7 @@
         <v>46199</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>46199</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>46202</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>46202</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>46204</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>46204</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>46205</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>46206</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>46206</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44704</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>46221</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>46224</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>46221</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>46221</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46222</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>46224</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46224</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46224</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>46273</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>46273</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>46273</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>46276</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44984,7 +44984,7 @@
         <v>46276</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>46276</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>46280</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>46280</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45296,7 +45296,7 @@
         <v>46279</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>46279</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>46279</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>46281</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>46281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>46287</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>46244</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>46246</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>46280</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>46244</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>46062</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>46248</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>46293</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>46253</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>46251</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>46295</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>46295</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>46295</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>46295</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
         <v>46289</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>46253</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>46289</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46289</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46289</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>46259</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>46302</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>46302</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>46259</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>46259</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>46302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>46302</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>46302</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>46302</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>46259</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45546</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>44601</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45195</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45678</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48266,7 +48266,7 @@
         <v>46089</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>46100</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45555</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45555</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45744</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44572</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45320</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45141</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>46062</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45720</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45845</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45539</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45943</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46043</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45320</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45324</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44504</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45446</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45001</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45884</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45744</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45936</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45958</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>45541</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45376</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46199</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45133</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45567</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>45799</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44732</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44951</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45014</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45118</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45183</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45317</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45559</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45232</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>46182</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45478</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>46196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>46100</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45075</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44935</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>46276</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>46239</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>46244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>46293</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45028</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>46062</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45799</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45370</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>46266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45880</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45883</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>46100</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44519</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44550</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44791</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44621</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44582</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44558</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44504</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44774</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44552</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44860</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44683</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44833</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44588</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44552</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44888</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44691</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44552</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44750</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44571</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44694</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44866</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44528</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44839</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44664</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44517</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44839</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44871</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44519</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44715</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44515</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44517</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44517</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44615</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44861</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44525</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44582</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44535</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>44615</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44749</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44522</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>44747</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>44552</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44880</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44517</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44839</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44732</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44879</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44722</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44713</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44515</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44819</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44879</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44545</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44505</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44551</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44546</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44829</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>44525</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44525</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44841</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44512</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45229</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45740</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45268</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45415</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>45093</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44831</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44957</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45641</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44531</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45604</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45769</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45617</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44957</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>44937</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45306</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44768</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44741</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45539</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44713</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44750</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>44749</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45336</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45183</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44874</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45674</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45643</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45229</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45258</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45609</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45506</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45506</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45506</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45506</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45506</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45293</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44951</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45232</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45467</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45527</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44896</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45432</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45282</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45610</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45751</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>44522</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44552</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>44995</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45629</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45086</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45002</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45461</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44818</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>44818</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45909</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45103</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44939</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45834</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45216</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>44768</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44799</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45095</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44719</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44552</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>44874</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45896</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45832</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45909</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45769</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45875</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45142</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>44994</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45818</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45356</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45593</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44671</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45443</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45905</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45876</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45079</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45909</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45896</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45909</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45909</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45366</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45169</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44620</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45040</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45916</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45916</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45076</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45337</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45589</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45456</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45099</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45929</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>46148</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45926</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>44708</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45936</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45372</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45315</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45943</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45943</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>44579</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44489</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45371</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44995</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>44502</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45405</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45260</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45260</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45425</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44592</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>46160</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>45960</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45960</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>46142</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45314</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45764</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45575</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45975</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45131</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44971</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44704</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45975</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45406</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44518</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45471</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45980</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45980</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45722</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45985</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44798</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45302</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45985</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45985</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44880</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45320</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45993</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45072</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45072</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45994</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45994</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45096</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>45092</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45994</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45029</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45631</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44852</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46171</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46171</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45617</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45281</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44742</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45527</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45593</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45278</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>46009</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45574</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45127</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>46017</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45643</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>46017</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>44575</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45471</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45533</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45232</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44861</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45195</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46030</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46030</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46030</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45315</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44552</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>46034</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45740</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45616</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>46044</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>46048</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45698</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45190</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44917</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45183</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45183</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44502</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46052</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44750</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44907</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>46183</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>46183</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>46058</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>46062</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>46061</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>46061</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>46061</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>46061</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>46061</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46061</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46061</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45154</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45229</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>44699</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46189</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45152</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46086</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45096</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46092</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45702</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>46098</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>46196</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46098</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46097</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45737</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45470</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45630</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45044</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45574</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>44910</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44893</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>46111</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>46111</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46111</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46112</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>46111</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45027</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45539</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>46174</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>46202</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>44530</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>46199</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>46126</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>44691</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>46199</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>46133</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46132</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45541</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45426</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45162</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45698</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45192</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>46204</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>45666</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45625</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>44704</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45467</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46206</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44888</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>46206</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>44540</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45007</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45007</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>44575</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>45619</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>44624</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44616</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>44719</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46221</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46221</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46222</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46221</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45609</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>46224</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>46224</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>46224</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>46224</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45350</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>46273</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45097</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>46273</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46273</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45007</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44788</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>44855</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>44992</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>44992</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44880</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>44749</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45618</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45281</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46279</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>44624</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>46276</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46276</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45506</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45233</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>46276</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>46279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>46279</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>44917</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>44957</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45167</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>46280</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46281</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45179</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>46280</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>46281</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44893</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45643</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>44750</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44904</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45769</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45179</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45769</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45644</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45647</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45596</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45253</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45405</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>46244</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>46244</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>44719</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45058</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>46281</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46246</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46280</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45728</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45211</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45365</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>44917</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45333</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>44818</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>44973</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>44694</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>46293</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44531</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45463</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>46248</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>46062</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>44596</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45720</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46251</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>44831</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>44964</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46295</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>46295</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>44893</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>44893</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46253</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45591</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46253</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>46289</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46295</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46289</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>46289</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45453</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45783</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>45783</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44846,7 +44846,7 @@
         <v>45541</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45281</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>44970</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45569</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45505</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45786</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46302</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46302</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45786</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>46302</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>46259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45786</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>46302</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>46259</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45734</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>46302</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>46302</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>46259</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>46259</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45793</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45769</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45793</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46307</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45726</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45085</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>46307</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45546</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45618</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45799</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46308</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>46311</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45818</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46310</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45643</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45825</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46309</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45835</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45866</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45834</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45680</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45834</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44972</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45876</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45880</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45568</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44601</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45195</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45195</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45678</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46089</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>46100</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45555</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45555</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45744</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>44572</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>45320</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45141</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>46062</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45720</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>45845</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45539</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45943</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46043</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>45320</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45324</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44504</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45446</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45001</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45884</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45744</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45936</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>45042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>45958</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45992</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>45541</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>45376</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46199</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45133</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45567</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44893</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>45799</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>44630</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44819</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>44995</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>44732</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44951</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45014</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45118</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45183</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45317</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45944</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45559</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45232</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45183</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>46182</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45478</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>46196</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>46100</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45075</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>45034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44935</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>46276</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>46239</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>46244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>46293</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45028</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>46062</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46303</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45799</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45370</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>46266</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45880</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>45883</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>46100</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44519</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44550</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44791</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44621</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44582</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44558</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11575,7 +11575,7 @@
         <v>44504</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>44774</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         <v>44552</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44860</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>44683</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44833</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>44588</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44552</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44888</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44691</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>44552</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44750</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44571</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44602</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44694</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44588</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44866</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44528</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44839</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44664</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44517</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44839</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44871</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>44519</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44715</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         <v>44515</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>44517</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44517</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44615</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>44861</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>44525</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44582</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14286,7 +14286,7 @@
         <v>44535</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14359,7 +14359,7 @@
         <v>44615</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>44749</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44522</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>44747</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>44552</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44880</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>44517</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>44839</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>44732</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>44879</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>44722</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44713</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15240,7 +15240,7 @@
         <v>44515</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44713</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15386,7 +15386,7 @@
         <v>44819</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44879</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44545</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44505</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44551</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>44546</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44829</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>44525</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>44525</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44841</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>44622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44512</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45229</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>45740</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45268</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45415</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>44487</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>45093</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>44599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>44831</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44957</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45641</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44531</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45604</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45769</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45617</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44957</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>44937</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45306</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44768</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44741</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45539</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>44713</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44750</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>44749</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45336</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45183</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44874</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45674</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45643</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45229</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45258</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45609</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45506</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>45506</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45506</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>45506</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45506</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45293</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>44951</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19562,7 +19562,7 @@
         <v>45232</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>45467</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45527</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>44896</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45432</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45282</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45610</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45751</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>44522</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44552</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>44995</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45629</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45086</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>45002</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45461</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44818</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>44818</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45909</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45103</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>44939</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45834</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45216</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21251,7 +21251,7 @@
         <v>44768</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>44799</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45095</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44719</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44552</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>44874</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45896</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45896</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45832</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45909</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45769</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45875</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45142</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>44994</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45818</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45356</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45593</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44671</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45443</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45905</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45876</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45079</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45909</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45896</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45909</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45909</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45366</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45169</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44620</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45040</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45916</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45916</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45076</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45337</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45589</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45456</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45099</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45929</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>46148</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45931</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45926</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>44708</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45936</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45372</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45315</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45943</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45943</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>44579</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>45736</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24994,7 +24994,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>44489</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45371</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44995</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>44502</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45405</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45260</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45260</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>45960</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45425</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>44592</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>46160</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>45960</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45960</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>46142</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45314</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45764</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45575</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45975</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45131</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>44971</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44704</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>45975</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46163</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45406</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44518</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45471</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45980</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45980</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45980</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>45722</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45985</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>45985</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44798</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45302</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45985</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45985</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44880</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45320</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45993</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45072</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45072</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45994</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45994</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45096</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>45092</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45994</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45029</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45631</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44852</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>46171</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>46171</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45617</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45281</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45281</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>44742</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45527</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>45593</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46009</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45278</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>46009</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45574</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45127</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>46017</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45643</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>46017</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>44575</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45471</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45533</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45232</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>44861</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45195</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30675,7 +30675,7 @@
         <v>46030</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>46030</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>46030</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>45315</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44552</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>46034</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>45740</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45616</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>46044</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>46048</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>45698</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45190</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44917</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45183</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45183</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>44502</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>46052</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31916,7 +31916,7 @@
         <v>44750</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>44907</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32062,7 +32062,7 @@
         <v>46183</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>46183</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32208,7 +32208,7 @@
         <v>46058</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>46062</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>46061</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>46061</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>46061</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>46061</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32646,7 +32646,7 @@
         <v>46061</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>46061</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>46061</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45070</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45154</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>45229</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>44699</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45034</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46189</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>45152</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         <v>46086</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33449,7 +33449,7 @@
         <v>45785</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45096</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46092</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45702</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>46098</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>46196</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>46098</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46097</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45737</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>45315</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>45470</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45630</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45044</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45574</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>44910</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>44893</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>46111</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>46111</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45098</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46111</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>46112</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>46111</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>45027</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45539</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>46174</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>46202</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>44530</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>46199</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>46126</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>44691</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>46202</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>46199</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>46133</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35888,7 +35888,7 @@
         <v>46132</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>45541</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>45426</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45162</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45698</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45192</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>46204</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>45666</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46204</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45625</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>44704</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>45467</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46206</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44888</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46205</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>46206</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37134,7 +37134,7 @@
         <v>44540</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>45007</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>45007</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37353,7 +37353,7 @@
         <v>44575</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37426,7 +37426,7 @@
         <v>45619</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>44624</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44616</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>44719</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46221</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46221</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46222</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37937,7 +37937,7 @@
         <v>46221</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45609</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38083,7 +38083,7 @@
         <v>46224</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>46224</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38229,7 +38229,7 @@
         <v>46224</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38302,7 +38302,7 @@
         <v>46224</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45350</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>46273</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45097</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>46273</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38677,7 +38677,7 @@
         <v>46273</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45007</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44788</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>44855</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38979,7 +38979,7 @@
         <v>44992</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>44992</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44880</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>44749</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>45618</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45281</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>46279</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>44624</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>46276</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>46276</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45506</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45233</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>46276</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39948,7 +39948,7 @@
         <v>46279</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>46279</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>44917</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>44957</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45167</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>46280</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40391,7 +40391,7 @@
         <v>46281</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45179</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>46280</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>46281</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44893</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>45643</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>44750</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>44904</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45769</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45179</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45769</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>45644</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45647</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>46287</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45596</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45253</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45405</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>46244</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>46244</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>44719</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45058</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>46281</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46246</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>46280</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>45728</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45211</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>45365</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>44917</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45333</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
         <v>44818</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>44973</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>44694</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45184</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>46293</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>44531</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42976,7 +42976,7 @@
         <v>45463</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>46248</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>46062</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43195,7 +43195,7 @@
         <v>44596</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43268,7 +43268,7 @@
         <v>45720</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>46251</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>44831</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>44964</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>46295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43638,7 +43638,7 @@
         <v>46295</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>46295</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>44893</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>44893</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>46253</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45591</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46253</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>45735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44237,7 +44237,7 @@
         <v>46289</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46295</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>46289</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>46289</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45453</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45783</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>45783</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44846,7 +44846,7 @@
         <v>45541</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45281</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>44970</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45569</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>45505</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45786</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46302</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46302</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>45786</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>46302</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>46259</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>45786</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>46302</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>46259</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45734</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>46302</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>46302</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>46259</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>46259</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45793</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45769</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45793</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>46307</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45726</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45085</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>46307</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45546</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45618</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45799</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46308</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>46311</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45818</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>46310</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>45643</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45825</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46309</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45835</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45866</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45834</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45680</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45834</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>44972</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45876</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45880</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45568</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44601</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>45195</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>45195</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45678</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>46089</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>46100</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45960</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45587</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45555</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45555</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45320</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46062</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45720</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>44572</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45744</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45943</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45539</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45320</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45446</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44504</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45324</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45884</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45376</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45936</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>44893</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45958</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>46199</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>45799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46313</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>46313</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45567</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45001</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44573</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45744</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45541</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44965</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44609</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44630</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44819</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44995</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45559</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45944</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46182</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44732</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45118</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45232</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>45370</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>46293</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>46100</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>46062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>46303</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45880</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45183</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44935</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45183</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>46313</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45028</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45075</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45014</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45478</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44756</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>45317</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46100</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44519</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44791</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44582</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44504</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44774</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44860</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44683</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44833</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44621</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44588</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44552</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44691</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44552</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44750</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>44571</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>44694</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44866</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44528</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44839</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44664</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44517</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>44502</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>44750</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44722</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44871</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44515</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44719</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44517</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44615</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44861</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44525</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44728</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44535</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44582</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44615</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44522</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44747</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44880</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44517</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44722</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44713</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44515</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44713</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44819</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44879</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44545</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44551</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44829</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44622</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44512</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45834</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45471</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45619</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>44742</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45593</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45337</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44874</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44552</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45591</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45896</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45183</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45425</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44750</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44616</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45443</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44823</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45905</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44691</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45072</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45072</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45909</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45866</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45909</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45876</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45909</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44624</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44531</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45589</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45916</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45916</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44995</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44995</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>46163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44964</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45040</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45736</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45470</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45541</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>44575</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>44957</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44957</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45154</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45926</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45929</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>46171</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45931</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45432</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45939</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45720</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44719</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45027</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45943</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45943</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45461</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45302</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45278</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45539</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45372</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>44893</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44893</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>44768</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45641</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44788</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>44741</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46183</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45142</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>46183</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45960</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45960</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45960</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45002</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45785</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46189</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45365</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45764</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>46196</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>44943</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>46174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>44592</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>46199</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46199</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45975</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45975</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45647</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44699</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45980</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>46202</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>46202</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45980</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45980</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45260</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45260</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45097</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45314</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46204</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45643</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45456</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45985</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>46204</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45985</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45229</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45985</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45985</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>46205</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45769</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>46206</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>46206</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44704</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45093</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45993</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45994</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45315</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45574</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>46221</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45184</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>46224</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46221</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>46221</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>46222</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46224</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>46224</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45453</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>46224</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45783</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45783</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45541</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>46009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46280</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>46280</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45786</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>46279</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>46279</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45281</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>46279</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>46009</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45786</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45786</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>46281</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>46017</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44970</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>46017</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>46281</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45533</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45505</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45569</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45734</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46030</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>46030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>46030</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>46034</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>45793</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45085</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>45793</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>46287</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45726</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45769</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>46244</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>46281</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>45618</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>46246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>46044</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>46048</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>46280</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>46244</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45799</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>46052</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>46058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>46062</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>46061</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>46061</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>46061</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46061</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>46061</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>46061</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>46061</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>46248</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>46293</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45818</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>46253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>46251</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>45643</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45825</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>46295</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>46295</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>46295</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>46086</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>44540</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45356</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>46295</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46289</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45835</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>46253</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>46289</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46092</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>46097</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>46289</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>46098</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>45162</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45845</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44893</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>46259</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>46302</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>46302</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46259</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>46259</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44888</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46111</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46111</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>46111</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>46302</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>46302</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>46302</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46111</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>46302</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>46259</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46112</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45866</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45834</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>44972</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45680</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45546</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45876</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45880</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>46307</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45568</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>46132</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>46307</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44893</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>44855</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>44874</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>46308</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46133</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44671</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44599</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45366</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45643</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45643</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45405</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>46310</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45698</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>46309</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>44818</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44917</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45618</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45007</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45007</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45604</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45666</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>44818</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44552</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>44910</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46311</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>44937</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>45832</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>45350</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45333</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>46314</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46314</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45092</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45232</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>46273</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45769</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45875</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45909</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45909</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45152</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>45195</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46273</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>46273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>46315</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45169</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45527</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>46276</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46276</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44596</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45818</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>44694</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>46276</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45698</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45229</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45609</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45751</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45506</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46142</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46160</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44798</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>44704</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45127</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45610</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45371</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>44917</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>44964</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44880</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45096</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45609</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45674</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>44768</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>44719</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44896</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44852</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44522</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45467</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44861</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45743</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45007</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45044</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45232</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45737</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45769</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45070</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45079</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45096</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44880</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45086</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45258</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45740</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>44531</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45099</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45596</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45617</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45002</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>45527</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44518</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45336</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45093</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>44502</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>44973</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>44831</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45769</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45593</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45575</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>45405</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>44951</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45574</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45281</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>44530</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>45617</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>45426</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45179</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45179</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45405</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45167</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45131</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45722</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45315</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45539</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45616</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45643</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45631</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45506</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45415</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>44579</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45625</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45506</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45506</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45506</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45506</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44624</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45281</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45281</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45098</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45095</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>45629</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>44708</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45133</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45190</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45192</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>44713</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45097</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>45183</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45183</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>44749</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45253</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>44749</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45463</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44750</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         <v>45306</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45735</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45702</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45315</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45740</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45320</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44917</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45233</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45229</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>44750</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>44904</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>44818</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>44994</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>44917</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>44939</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45728</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45644</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45293</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>45076</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>44502</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>44620</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45406</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45216</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>44799</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45630</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45211</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45471</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>44719</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>44907</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>44552</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>44957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>44575</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>44831</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>44992</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44992</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>44601</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45195</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45195</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45678</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>46089</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>46100</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>

--- a/Översikt SALA.xlsx
+++ b/Översikt SALA.xlsx
@@ -601,7 +601,7 @@
         <v>44995</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         <v>46092</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45446</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>45548</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44608</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45960</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45713</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45587</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>45555</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>45555</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>45097</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45576</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>45320</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>45845</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>46062</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45720</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>44572</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45744</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>44154</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45943</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45539</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45161</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>45107</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>45320</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45446</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>46106</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>46043</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44504</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45324</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44546</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45884</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45376</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45936</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>44893</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45958</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45042</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>46199</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>45799</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>46313</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>46313</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45567</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>45001</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45133</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44573</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45744</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45541</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>44965</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>44879</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44609</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>44837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44630</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44819</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44995</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45559</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45944</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>45944</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46182</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>45958</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44732</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>46196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45118</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45232</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>46244</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>45370</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>46293</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>46100</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>46062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>46303</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45880</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45183</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44935</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>46266</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45183</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>46313</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>46276</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44951</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45028</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45075</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45014</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45478</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44756</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>45317</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46100</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44550</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44519</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44552</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44791</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44552</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44582</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44558</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44504</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44774</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44552</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44860</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44683</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44833</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44621</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44588</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44552</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44888</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44691</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>44552</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44750</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>44571</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>44694</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44866</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44528</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44839</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>44664</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>44517</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>44502</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>44750</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>44722</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44871</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>44519</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44715</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44515</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44719</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44517</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44517</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>44615</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>44861</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44525</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44728</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44535</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44582</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44615</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44749</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44522</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44747</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44880</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44732</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44517</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44722</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44713</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44515</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44713</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44819</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44879</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44505</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44545</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44551</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44829</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44525</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44525</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44841</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44622</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44512</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>45834</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45471</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16725,7 +16725,7 @@
         <v>45619</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>44742</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45593</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45337</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44874</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44552</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45591</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45896</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45896</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45183</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>45467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45425</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44750</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44616</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45443</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44823</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45905</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44691</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45072</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45072</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45909</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45866</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45909</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45876</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45896</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>45909</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45909</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44624</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44531</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45589</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45916</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45916</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44995</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44995</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>46163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>44964</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45040</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45736</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45470</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45541</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>44575</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>44957</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44957</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>45154</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45926</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20093,7 +20093,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>45929</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>46171</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45931</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>45936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45432</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45939</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45720</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44719</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45027</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45943</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45943</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45461</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45302</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45278</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>45539</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45372</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>44893</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44893</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>44768</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21631,7 +21631,7 @@
         <v>45641</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44788</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>44741</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>46183</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45142</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>46183</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45960</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45960</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45960</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>45002</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45785</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45544</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>46189</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45365</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>45764</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45103</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>46196</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45029</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>44943</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>46174</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>44592</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>46199</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>46199</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45975</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>45975</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45647</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>44699</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45980</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>46202</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>46202</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45980</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45980</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45260</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45260</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45097</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45314</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46204</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45643</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45456</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45985</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>46204</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45985</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45229</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45985</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45985</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>46205</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45769</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>46206</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>46206</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44704</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45093</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45993</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45994</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45315</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45574</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>46221</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45184</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>46224</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46221</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>46221</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>46222</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46224</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>46224</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>45453</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>46224</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45783</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45783</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45541</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>46009</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46280</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>46280</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45786</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>46279</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>46279</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>45281</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>46279</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>46009</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>45786</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>45786</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>46281</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>46017</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>44970</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>46017</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>46281</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45533</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45505</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45569</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45734</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46030</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>46030</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>46030</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>46034</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>45793</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>45085</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>45793</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>46287</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45726</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45769</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>46244</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>46281</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>45618</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>46246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>46044</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>46048</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>46280</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>46244</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45799</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>46052</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>46058</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>46062</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>46061</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>46061</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>46061</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46061</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>46061</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>46061</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>46061</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>46062</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>46248</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>46293</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45818</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>46253</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>46251</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>45643</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45825</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>46295</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>46295</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31445,7 +31445,7 @@
         <v>46295</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>46086</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31596,7 +31596,7 @@
         <v>44540</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45356</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>46295</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46289</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45835</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>46253</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>46289</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>46092</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>46097</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>46289</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>46098</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46098</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>45162</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45845</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44893</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>46259</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>46302</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>46302</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46259</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>46259</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44888</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46111</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46111</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>46111</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>46302</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>46302</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>46302</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46111</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>46302</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>46259</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>46112</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45866</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>45834</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45834</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>44972</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45680</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45546</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45876</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45880</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>46307</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45568</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>46132</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>46307</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>44893</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>44855</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>44874</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>46308</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46133</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44671</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>44599</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>45366</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45643</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45643</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45405</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>46310</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45698</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>46309</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>44818</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44917</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>45618</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45007</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45007</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45604</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45666</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>44818</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44552</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>44910</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46311</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>44937</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36849,7 +36849,7 @@
         <v>45832</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36922,7 +36922,7 @@
         <v>45350</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45333</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37068,7 +37068,7 @@
         <v>46314</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46314</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45092</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45232</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>46273</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45769</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45875</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45909</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45909</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45152</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>45195</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46273</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>46273</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>46315</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>45169</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45527</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>46276</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>46276</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>44596</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45818</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>44694</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>46276</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46148</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45698</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>45229</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45609</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>45751</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45506</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46142</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46160</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>44798</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39371,7 +39371,7 @@
         <v>44704</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45127</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>45610</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>45371</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>44917</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>44964</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44880</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>45096</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39960,7 +39960,7 @@
         <v>45609</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45674</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>44768</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>44719</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>44896</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44852</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40398,7 +40398,7 @@
         <v>44522</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40471,7 +40471,7 @@
         <v>45467</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>44861</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45743</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45007</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40763,7 +40763,7 @@
         <v>45044</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45232</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45737</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45769</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45070</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41133,7 +41133,7 @@
         <v>45079</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45096</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44880</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>45086</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         <v>45258</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45740</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>44531</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41654,7 +41654,7 @@
         <v>45099</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45596</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45617</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41873,7 +41873,7 @@
         <v>45002</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41946,7 +41946,7 @@
         <v>45527</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44518</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45336</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45093</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>44502</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>44973</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>44831</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45769</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45593</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45575</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>45405</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>44951</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45574</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45281</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>44530</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45282</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>45617</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>45426</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45179</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45179</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45405</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45167</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45131</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45722</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45315</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45539</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45616</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45643</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45631</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>45506</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>45415</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>44579</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45625</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>45506</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45506</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45506</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45506</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         <v>44624</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45281</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45281</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44866,7 +44866,7 @@
         <v>45098</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45095</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45012,7 +45012,7 @@
         <v>45629</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>44708</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45158,7 +45158,7 @@
         <v>45133</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45190</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45304,7 +45304,7 @@
         <v>45192</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>44713</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>45097</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>45183</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45183</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>44749</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45253</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>44749</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45463</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>44750</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         <v>45306</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45735</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45702</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46263,7 +46263,7 @@
         <v>45315</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45740</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45320</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46487,7 +46487,7 @@
         <v>44917</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45233</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46633,7 +46633,7 @@
         <v>45229</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46706,7 +46706,7 @@
         <v>44750</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>44904</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>44818</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>44994</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47003,7 +47003,7 @@
         <v>44917</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>44939</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45728</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47222,7 +47222,7 @@
         <v>45644</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>45293</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>45076</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>44502</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>44620</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45406</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45216</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>44799</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45630</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45211</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45471</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>44719</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>44907</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>44552</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>44957</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>44575</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>44831</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>44992</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>44992</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>44601</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48687,7 +48687,7 @@
         <v>45195</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>45195</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45678</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>46089</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>46100</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
